--- a/data/trans_dic/P2C_R1-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R1-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados</t>
+          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados (tasa de respuesta: 98,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,71</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,36</t>
+          <t>0,76; 3,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,59; 35,23</t>
+          <t>19,12; 33,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,65</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,34</t>
+          <t>0,4; 2,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,47</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,95; 32,93</t>
+          <t>22,19; 32,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,26</t>
+          <t>0,12; 1,18</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,67</t>
+          <t>0,36; 1,7</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,83</t>
+          <t>0,5; 1,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,01; 30,97</t>
+          <t>22,03; 31,43</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,4</t>
+          <t>0,18; 2,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,32</t>
+          <t>0,15; 1,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,79</t>
+          <t>0,0; 1,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,47; 20,91</t>
+          <t>9,59; 21,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,38</t>
+          <t>0,48; 2,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,61</t>
+          <t>0,15; 1,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,8</t>
+          <t>0,29; 1,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,07; 19,12</t>
+          <t>12,2; 19,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,76</t>
+          <t>0,39; 1,73</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,23</t>
+          <t>0,24; 1,24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,31</t>
+          <t>0,25; 1,23</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,14; 18,22</t>
+          <t>11,96; 18,17</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,85</t>
+          <t>0,22; 2,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,75</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,67; 23,8</t>
+          <t>9,05; 24,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,82</t>
+          <t>0,21; 1,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,47</t>
+          <t>0,4; 2,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,58</t>
+          <t>0,45; 2,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 12,24</t>
+          <t>1,19; 12,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,97</t>
+          <t>0,11; 0,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,08</t>
+          <t>0,5; 2,02</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,93</t>
+          <t>0,46; 1,74</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 14,3</t>
+          <t>2,18; 14,55</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,91</t>
+          <t>0,34; 1,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,67</t>
+          <t>0,35; 2,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,38</t>
+          <t>0,52; 2,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,51; 18,88</t>
+          <t>8,37; 19,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,8</t>
+          <t>0,18; 1,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,08</t>
+          <t>0,95; 3,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,5</t>
+          <t>0,61; 2,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,43; 22,84</t>
+          <t>13,52; 22,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,44</t>
+          <t>0,36; 1,47</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,32</t>
+          <t>0,85; 2,29</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,08</t>
+          <t>0,69; 2,18</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,52; 19,4</t>
+          <t>12,43; 19,63</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,08</t>
+          <t>0,29; 1,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,25</t>
+          <t>0,46; 1,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,43</t>
+          <t>0,57; 1,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,68; 20,03</t>
+          <t>13,65; 20,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,29</t>
+          <t>0,44; 1,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,66</t>
+          <t>0,72; 1,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,54</t>
+          <t>0,64; 1,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,46; 18,09</t>
+          <t>7,22; 18,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,06</t>
+          <t>0,44; 0,98</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,32</t>
+          <t>0,68; 1,32</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,29</t>
+          <t>0,66; 1,29</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,67; 17,71</t>
+          <t>8,58; 17,73</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados</t>
+          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados (tasa de respuesta: 98,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 7239</t>
+          <t>0; 7165</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6653</t>
+          <t>0; 7994</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3001; 13361</t>
+          <t>3014; 13949</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19631; 35309</t>
+          <t>19160; 33825</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 8140</t>
+          <t>0; 8046</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2125; 12042</t>
+          <t>2051; 12271</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6559</t>
+          <t>0; 6588</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>29843; 44773</t>
+          <t>30162; 43738</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1199; 11554</t>
+          <t>1127; 10796</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3278; 16488</t>
+          <t>3529; 16771</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3883; 15491</t>
+          <t>4212; 16416</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>51991; 73151</t>
+          <t>52038; 74228</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1064; 14072</t>
+          <t>1058; 13807</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>954; 8702</t>
+          <t>962; 8670</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 10407</t>
+          <t>0; 8514</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15302; 33792</t>
+          <t>15490; 33945</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2762; 15465</t>
+          <t>3106; 15774</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1101; 11997</t>
+          <t>1102; 13402</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2075; 12900</t>
+          <t>2065; 11756</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29590; 46871</t>
+          <t>29900; 46988</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5793; 21776</t>
+          <t>4765; 21333</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3649; 17336</t>
+          <t>3397; 17443</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3247; 17007</t>
+          <t>3227; 16027</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>49359; 74122</t>
+          <t>48651; 73907</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2011</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1811; 13024</t>
+          <t>988; 12748</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 7295</t>
+          <t>0; 7853</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8779; 24111</t>
+          <t>9172; 24478</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>964; 8674</t>
+          <t>976; 8795</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2086; 13142</t>
+          <t>2120; 14214</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2307; 13245</t>
+          <t>2312; 13882</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2851; 40771</t>
+          <t>3960; 43165</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>976; 8488</t>
+          <t>978; 8739</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4998; 20561</t>
+          <t>4948; 19981</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4252; 17974</t>
+          <t>4240; 16140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8308; 62122</t>
+          <t>9461; 63213</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1680; 9491</t>
+          <t>1696; 9545</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1923; 14581</t>
+          <t>1915; 13697</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2277; 11900</t>
+          <t>2604; 12455</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10727; 23808</t>
+          <t>10563; 24979</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1653; 12300</t>
+          <t>1229; 12125</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6819; 22268</t>
+          <t>6855; 22420</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3663; 16485</t>
+          <t>4009; 17422</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24530; 41705</t>
+          <t>24682; 40871</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4432; 16990</t>
+          <t>4216; 17337</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10904; 29516</t>
+          <t>10739; 29038</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8343; 24140</t>
+          <t>8052; 25271</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>38637; 59887</t>
+          <t>38359; 60599</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4736; 20677</t>
+          <t>5479; 20075</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9457; 26765</t>
+          <t>9727; 28419</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10603; 27109</t>
+          <t>10835; 27175</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>66947; 97983</t>
+          <t>66767; 99445</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10664; 29730</t>
+          <t>10194; 28173</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18997; 41757</t>
+          <t>18056; 41584</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14413; 35890</t>
+          <t>14921; 33490</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>57911; 162248</t>
+          <t>64709; 162854</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19490; 44763</t>
+          <t>18664; 41428</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32174; 61541</t>
+          <t>31692; 61375</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29413; 54728</t>
+          <t>28035; 54523</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>120183; 245408</t>
+          <t>118878; 245815</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R1-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R1-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>25,88%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,51</t>
+          <t>0,72; 3,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,12; 33,75</t>
+          <t>18,15; 34,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,38</t>
+          <t>0,38; 2,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,19; 32,17</t>
+          <t>21,43; 32,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,18</t>
+          <t>0,12; 1,08</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,7</t>
+          <t>0,38; 1,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,94</t>
+          <t>0,52; 2,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,03; 31,43</t>
+          <t>21,01; 30,29</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,35</t>
+          <t>0,18; 2,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,31</t>
+          <t>0,14; 1,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,46</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,59; 21,01</t>
+          <t>8,6; 19,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,43</t>
+          <t>0,52; 2,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,79</t>
+          <t>0,15; 1,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,64</t>
+          <t>0,29; 1,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,2; 19,17</t>
+          <t>11,63; 18,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,73</t>
+          <t>0,49; 1,79</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,24</t>
+          <t>0,22; 1,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,23</t>
+          <t>0,26; 1,23</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,96; 18,17</t>
+          <t>11,44; 17,29</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -1002,57 +1002,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,79</t>
+          <t>0,4; 2,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,05; 24,16</t>
+          <t>8,15; 22,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,85</t>
+          <t>0,2; 1,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,67</t>
+          <t>0,4; 2,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,7</t>
+          <t>0,45; 2,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 12,96</t>
+          <t>7,67; 15,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,99</t>
+          <t>0,11; 0,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,02</t>
+          <t>0,5; 2,05</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,74</t>
+          <t>0,43; 1,83</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 14,55</t>
+          <t>8,98; 16,63</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,92</t>
+          <t>0,34; 1,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,51</t>
+          <t>0,35; 2,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,49</t>
+          <t>0,47; 2,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,37; 19,8</t>
+          <t>7,02; 17,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,78</t>
+          <t>0,15; 1,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,1</t>
+          <t>0,95; 3,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,65</t>
+          <t>0,59; 2,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,52; 22,38</t>
+          <t>12,57; 21,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,47</t>
+          <t>0,43; 1,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,29</t>
+          <t>0,84; 2,32</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,18</t>
+          <t>0,72; 2,01</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,43; 19,63</t>
+          <t>11,37; 17,96</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>16,02%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,05</t>
+          <t>0,32; 1,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,33</t>
+          <t>0,44; 1,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,43</t>
+          <t>0,55; 1,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,65; 20,33</t>
+          <t>12,54; 18,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,22</t>
+          <t>0,46; 1,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,65</t>
+          <t>0,78; 1,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,43</t>
+          <t>0,63; 1,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,22; 18,16</t>
+          <t>14,65; 18,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,98</t>
+          <t>0,44; 0,99</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,32</t>
+          <t>0,7; 1,35</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,29</t>
+          <t>0,69; 1,33</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,58; 17,73</t>
+          <t>14,42; 17,87</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>27196</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>36452</t>
+          <t>39132</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>62640</t>
+          <t>66328</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 7165</t>
+          <t>0; 7229</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 7994</t>
+          <t>0; 7383</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3014; 13949</t>
+          <t>2873; 14126</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19160; 33825</t>
+          <t>19702; 37110</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 8046</t>
+          <t>0; 8210</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2051; 12271</t>
+          <t>1935; 12057</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6588</t>
+          <t>0; 6143</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30162; 43738</t>
+          <t>31661; 47284</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1127; 10796</t>
+          <t>1124; 9842</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3529; 16771</t>
+          <t>3710; 16321</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4212; 16416</t>
+          <t>4392; 16853</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>52038; 74228</t>
+          <t>53841; 77652</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23271</t>
+          <t>24923</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>37569</t>
+          <t>40114</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>60840</t>
+          <t>65037</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1058; 13807</t>
+          <t>1058; 13934</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>962; 8670</t>
+          <t>957; 9441</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 8514</t>
+          <t>0; 8941</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15490; 33945</t>
+          <t>16644; 37563</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3106; 15774</t>
+          <t>3382; 16382</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1102; 13402</t>
+          <t>1111; 12396</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2065; 11756</t>
+          <t>2114; 12417</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29900; 46988</t>
+          <t>31923; 50819</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4765; 21333</t>
+          <t>6010; 22154</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3397; 17443</t>
+          <t>3086; 16769</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3227; 16027</t>
+          <t>3336; 15973</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>48651; 73907</t>
+          <t>53530; 80911</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15502</t>
+          <t>16266</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14325</t>
+          <t>17697</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29827</t>
+          <t>33963</t>
         </is>
       </c>
     </row>
@@ -2066,57 +2066,57 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>988; 12748</t>
+          <t>1824; 12066</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 7853</t>
+          <t>0; 7230</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9172; 24478</t>
+          <t>9515; 25987</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>976; 8795</t>
+          <t>973; 8730</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2120; 14214</t>
+          <t>2111; 13993</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2312; 13882</t>
+          <t>2304; 14159</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3960; 43165</t>
+          <t>11955; 24716</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>978; 8739</t>
+          <t>975; 8586</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4948; 19981</t>
+          <t>4962; 20309</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4240; 16140</t>
+          <t>4033; 16966</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9461; 63213</t>
+          <t>24473; 45319</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16373</t>
+          <t>16443</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>31937</t>
+          <t>34624</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>48310</t>
+          <t>51067</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1696; 9545</t>
+          <t>1700; 9312</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1915; 13697</t>
+          <t>1932; 14118</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2604; 12455</t>
+          <t>2343; 12368</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10563; 24979</t>
+          <t>9970; 24245</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1229; 12125</t>
+          <t>1034; 12351</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6855; 22420</t>
+          <t>6870; 22539</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4009; 17422</t>
+          <t>3914; 16712</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24682; 40871</t>
+          <t>26603; 45721</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4216; 17337</t>
+          <t>5026; 18832</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10739; 29038</t>
+          <t>10724; 29452</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8052; 25271</t>
+          <t>8302; 23264</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>38359; 60599</t>
+          <t>40219; 63514</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>81334</t>
+          <t>84828</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>120283</t>
+          <t>131567</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>201617</t>
+          <t>216395</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5479; 20075</t>
+          <t>6058; 20774</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9727; 28419</t>
+          <t>9478; 27855</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10835; 27175</t>
+          <t>10481; 28089</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>66767; 99445</t>
+          <t>70340; 105299</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10194; 28173</t>
+          <t>10648; 29809</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18056; 41584</t>
+          <t>19644; 43059</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14921; 33490</t>
+          <t>14748; 33957</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>64709; 162854</t>
+          <t>115664; 147593</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18664; 41428</t>
+          <t>18714; 41885</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31692; 61375</t>
+          <t>32674; 62658</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28035; 54523</t>
+          <t>29164; 56166</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>118878; 245815</t>
+          <t>194694; 241368</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R1-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R1-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados (tasa de respuesta: 98,16%)</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son remunerados (tasa de respuesta: 98,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados (tasa de respuesta: 98,16%)</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son remunerados (tasa de respuesta: 98,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
